--- a/こころ住設_案件管理シート_叩き台.xlsx
+++ b/こころ住設_案件管理シート_叩き台.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="P3" s="17" t="inlineStr">
         <is>
-          <t>交換</t>
+          <t>交換・修理</t>
         </is>
       </c>
       <c r="Q3" s="17" t="n"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P4" s="17" t="inlineStr">
         <is>
-          <t>交換</t>
+          <t>交換・修理</t>
         </is>
       </c>
       <c r="Q4" s="17" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t>水漏れ・詰まり</t>
+          <t>緊急対応</t>
         </is>
       </c>
       <c r="Q5" s="17" t="n"/>
@@ -1292,10 +1292,10 @@
       <formula1>選択肢!$I$2:$I$6</formula1>
     </dataValidation>
     <dataValidation sqref="O3:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$J$2:$J$9</formula1>
+      <formula1>選択肢!$J$2:$J$10</formula1>
     </dataValidation>
     <dataValidation sqref="P3:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$K$2:$K$5</formula1>
+      <formula1>選択肢!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="R3:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>選択肢!$L$2:$L$3</formula1>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>トイレ／キッチン／浴室・給湯器／洗面・蛇口／換気扇／電気／ガスコンロ・食洗機／その他（分類は木場さんが叩き台を作成中）</t>
+          <t>トイレ／キッチン／給湯器／換気扇／風呂／その他水回り／水栓・蛇口／電気関係／その他（清水様の工事可能品目の区分）</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>交換／修理／水漏れ・詰まり／その他</t>
+          <t>交換・修理／水漏れ／緊急対応。換気扇・電気関係は交換・修理のみ</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>例：壁紙・床の張り替えも希望</t>
+          <t>お客様が品目まで話した場合にメモ（例：ウォシュレット交換、手すり設置も）</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>交換</t>
+          <t>交換・修理</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>修理</t>
+          <t>水漏れ</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>浴室・給湯器</t>
+          <t>給湯器</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>水漏れ・詰まり</t>
+          <t>緊急対応</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2945,12 +2945,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>洗面・蛇口</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>その他</t>
+          <t>換気扇</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2977,7 +2972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>換気扇</t>
+          <t>風呂</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2994,7 +2989,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>電気</t>
+          <t>その他水回り</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3001,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ガスコンロ・食洗機</t>
+          <t>水栓・蛇口</t>
         </is>
       </c>
     </row>
@@ -3017,6 +3012,13 @@
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>電気関係</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="J10" t="inlineStr">
         <is>
           <t>その他</t>
         </is>

--- a/こころ住設_案件管理シート_叩き台.xlsx
+++ b/こころ住設_案件管理シート_叩き台.xlsx
@@ -73,7 +73,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -95,64 +95,23 @@
         <color rgb="00C9D2D8"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C9D2D8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C9D2D8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C9D2D8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00C9D2D8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9D2D8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00C9D2D8"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C9D2D8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9D2D8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -543,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -551,22 +510,22 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
@@ -575,8 +534,7 @@
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -589,576 +547,548 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>案件の基本</t>
         </is>
       </c>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>問い合わせ内容</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="n"/>
+      <c r="O1" s="6" t="n"/>
+      <c r="P1" s="6" t="n"/>
+      <c r="Q1" s="6" t="n"/>
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>写真</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>見積もり</t>
         </is>
       </c>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="3" t="n"/>
-      <c r="X1" s="8" t="inlineStr">
+      <c r="T1" s="9" t="n"/>
+      <c r="U1" s="9" t="n"/>
+      <c r="V1" s="9" t="n"/>
+      <c r="W1" s="10" t="inlineStr">
         <is>
           <t>工事・集金</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="3" t="n"/>
-      <c r="AE1" s="6" t="inlineStr">
+      <c r="X1" s="11" t="n"/>
+      <c r="Y1" s="11" t="n"/>
+      <c r="Z1" s="11" t="n"/>
+      <c r="AA1" s="11" t="n"/>
+      <c r="AB1" s="11" t="n"/>
+      <c r="AC1" s="11" t="n"/>
+      <c r="AD1" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>お名前</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>電話番号</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>電話の種類</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>新規／リピート</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>工番</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>前回の工番</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>受付日時</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>受付経路</t>
-        </is>
-      </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>対応担当者</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr">
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>折り返し理由</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="M2" s="14" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="N2" s="14" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="O2" s="14" t="inlineStr">
         <is>
           <t>複数箇所</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="P2" s="14" t="inlineStr">
         <is>
           <t>ご用件メモ</t>
         </is>
       </c>
-      <c r="R2" s="11" t="inlineStr">
+      <c r="Q2" s="14" t="inlineStr">
         <is>
           <t>緊急訪問の希望</t>
         </is>
       </c>
-      <c r="S2" s="12" t="inlineStr">
+      <c r="R2" s="15" t="inlineStr">
         <is>
           <t>写真フォルダ</t>
         </is>
       </c>
-      <c r="T2" s="13" t="inlineStr">
+      <c r="S2" s="16" t="inlineStr">
         <is>
           <t>見積訪問日</t>
         </is>
       </c>
-      <c r="U2" s="13" t="inlineStr">
+      <c r="T2" s="16" t="inlineStr">
         <is>
           <t>見積訪問時間</t>
         </is>
       </c>
-      <c r="V2" s="13" t="inlineStr">
+      <c r="U2" s="16" t="inlineStr">
         <is>
           <t>見積担当</t>
         </is>
       </c>
-      <c r="W2" s="13" t="inlineStr">
+      <c r="V2" s="16" t="inlineStr">
         <is>
           <t>見積金額</t>
         </is>
       </c>
-      <c r="X2" s="14" t="inlineStr">
+      <c r="W2" s="17" t="inlineStr">
         <is>
           <t>工事日</t>
         </is>
       </c>
-      <c r="Y2" s="14" t="inlineStr">
+      <c r="X2" s="17" t="inlineStr">
         <is>
           <t>工事時間</t>
         </is>
       </c>
-      <c r="Z2" s="14" t="inlineStr">
+      <c r="Y2" s="17" t="inlineStr">
         <is>
           <t>工事担当</t>
         </is>
       </c>
-      <c r="AA2" s="14" t="inlineStr">
+      <c r="Z2" s="17" t="inlineStr">
         <is>
           <t>訪問回数</t>
         </is>
       </c>
-      <c r="AB2" s="14" t="inlineStr">
+      <c r="AA2" s="17" t="inlineStr">
         <is>
           <t>集金金額</t>
         </is>
       </c>
-      <c r="AC2" s="14" t="inlineStr">
+      <c r="AB2" s="17" t="inlineStr">
         <is>
           <t>集金方法</t>
         </is>
       </c>
-      <c r="AD2" s="14" t="inlineStr">
+      <c r="AC2" s="17" t="inlineStr">
         <is>
           <t>集金状況</t>
         </is>
       </c>
-      <c r="AE2" s="12" t="inlineStr">
+      <c r="AD2" s="15" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>【サンプル】山田 花子</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>090-xxxx-xxxx</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>◯◯市◯◯町2-2-3</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>ヤマダ ハナコ</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>携帯</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
-      <c r="G3" s="15" t="n">
+      <c r="G3" s="18" t="n">
         <v>1001</v>
       </c>
-      <c r="H3" s="15" t="n"/>
-      <c r="I3" s="15" t="inlineStr">
+      <c r="H3" s="18" t="n"/>
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>2026/10/06 10:12</t>
         </is>
       </c>
-      <c r="J3" s="15" t="inlineStr">
-        <is>
-          <t>受電AI</t>
-        </is>
-      </c>
-      <c r="K3" s="15" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>受付（見積前）</t>
         </is>
       </c>
-      <c r="L3" s="15" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>清水</t>
         </is>
       </c>
-      <c r="M3" s="15" t="n"/>
-      <c r="N3" s="15" t="inlineStr">
+      <c r="L3" s="18" t="n"/>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>トイレ</t>
         </is>
       </c>
-      <c r="O3" s="15" t="inlineStr">
+      <c r="N3" s="18" t="inlineStr">
         <is>
           <t>交換・修理</t>
         </is>
       </c>
-      <c r="P3" s="15" t="inlineStr">
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t>いいえ</t>
         </is>
       </c>
-      <c r="Q3" s="15" t="inlineStr">
+      <c r="P3" s="18" t="inlineStr">
         <is>
           <t>古くなったのでトイレ本体のみ交換したい</t>
         </is>
       </c>
-      <c r="R3" s="15" t="inlineStr">
+      <c r="Q3" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="S3" s="15" t="n"/>
-      <c r="T3" s="15" t="inlineStr">
+      <c r="R3" s="18" t="n"/>
+      <c r="S3" s="18" t="inlineStr">
         <is>
           <t>2026/10/09</t>
         </is>
       </c>
-      <c r="U3" s="15" t="inlineStr">
+      <c r="T3" s="18" t="inlineStr">
         <is>
           <t>10:00-11:00</t>
         </is>
       </c>
-      <c r="V3" s="15" t="inlineStr">
+      <c r="U3" s="18" t="inlineStr">
         <is>
           <t>清水</t>
         </is>
       </c>
-      <c r="W3" s="15" t="n"/>
-      <c r="X3" s="15" t="n"/>
-      <c r="Y3" s="15" t="n"/>
-      <c r="Z3" s="15" t="n"/>
-      <c r="AA3" s="15" t="n">
+      <c r="V3" s="18" t="n"/>
+      <c r="W3" s="18" t="n"/>
+      <c r="X3" s="18" t="n"/>
+      <c r="Y3" s="18" t="n"/>
+      <c r="Z3" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="AB3" s="15" t="n"/>
-      <c r="AC3" s="15" t="n"/>
-      <c r="AD3" s="15" t="n"/>
-      <c r="AE3" s="15" t="n"/>
+      <c r="AA3" s="18" t="n"/>
+      <c r="AB3" s="18" t="n"/>
+      <c r="AC3" s="18" t="n"/>
+      <c r="AD3" s="18" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>【サンプル】佐藤 一郎</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>03-xxxx-xxxx</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>◯◯市◯◯町3-4-5</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>サトウ イチロウ</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>固定</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
-      <c r="G4" s="15" t="n">
+      <c r="G4" s="18" t="n">
         <v>1002</v>
       </c>
-      <c r="H4" s="15" t="n"/>
-      <c r="I4" s="15" t="inlineStr">
+      <c r="H4" s="18" t="n"/>
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>2026/10/06 11:40</t>
         </is>
       </c>
-      <c r="J4" s="15" t="inlineStr">
-        <is>
-          <t>受電AI</t>
-        </is>
-      </c>
-      <c r="K4" s="15" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>折り返し待ち</t>
         </is>
       </c>
-      <c r="L4" s="15" t="n"/>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="K4" s="18" t="n"/>
+      <c r="L4" s="18" t="inlineStr">
         <is>
           <t>複数箇所</t>
         </is>
       </c>
-      <c r="N4" s="15" t="inlineStr">
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="O4" s="15" t="inlineStr">
+      <c r="N4" s="18" t="inlineStr">
         <is>
           <t>交換・修理</t>
         </is>
       </c>
-      <c r="P4" s="15" t="inlineStr">
+      <c r="O4" s="18" t="inlineStr">
         <is>
           <t>はい</t>
         </is>
       </c>
-      <c r="Q4" s="15" t="inlineStr">
+      <c r="P4" s="18" t="inlineStr">
         <is>
           <t>トイレ、キッチン、洗面所の蛇口を見てほしい</t>
         </is>
       </c>
-      <c r="R4" s="15" t="inlineStr">
+      <c r="Q4" s="18" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="S4" s="15" t="n"/>
-      <c r="T4" s="15" t="n"/>
-      <c r="U4" s="15" t="n"/>
-      <c r="V4" s="15" t="n"/>
-      <c r="W4" s="15" t="n"/>
-      <c r="X4" s="15" t="n"/>
-      <c r="Y4" s="15" t="n"/>
-      <c r="Z4" s="15" t="n"/>
-      <c r="AA4" s="15" t="n">
+      <c r="R4" s="18" t="n"/>
+      <c r="S4" s="18" t="n"/>
+      <c r="T4" s="18" t="n"/>
+      <c r="U4" s="18" t="n"/>
+      <c r="V4" s="18" t="n"/>
+      <c r="W4" s="18" t="n"/>
+      <c r="X4" s="18" t="n"/>
+      <c r="Y4" s="18" t="n"/>
+      <c r="Z4" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" s="15" t="n"/>
-      <c r="AC4" s="15" t="n"/>
-      <c r="AD4" s="15" t="n"/>
-      <c r="AE4" s="15" t="n"/>
+      <c r="AA4" s="18" t="n"/>
+      <c r="AB4" s="18" t="n"/>
+      <c r="AC4" s="18" t="n"/>
+      <c r="AD4" s="18" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>【サンプル】山田 太郎</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>090-xxxx-xxxx</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>◯◯市◯◯町2-2-3</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>ヤマダ タロウ</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>携帯</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>リピート</t>
         </is>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="18" t="n">
         <v>1003</v>
       </c>
-      <c r="H5" s="15" t="n">
+      <c r="H5" s="18" t="n">
         <v>1001</v>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>2026/10/06 13:05</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>受電AI</t>
-        </is>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>工事完了</t>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr">
+      <c r="K5" s="18" t="inlineStr">
         <is>
           <t>担当者B</t>
         </is>
       </c>
-      <c r="M5" s="15" t="inlineStr">
+      <c r="L5" s="18" t="inlineStr">
         <is>
           <t>緊急訪問希望</t>
         </is>
       </c>
-      <c r="N5" s="15" t="inlineStr">
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="O5" s="15" t="inlineStr">
+      <c r="N5" s="18" t="inlineStr">
         <is>
           <t>緊急対応</t>
         </is>
       </c>
-      <c r="P5" s="15" t="inlineStr">
+      <c r="O5" s="18" t="inlineStr">
         <is>
           <t>いいえ</t>
         </is>
       </c>
-      <c r="Q5" s="15" t="inlineStr">
+      <c r="P5" s="18" t="inlineStr">
         <is>
           <t>キッチン下の収納の中で水漏れ</t>
         </is>
       </c>
-      <c r="R5" s="15" t="inlineStr">
+      <c r="Q5" s="18" t="inlineStr">
         <is>
           <t>あり</t>
         </is>
       </c>
-      <c r="S5" s="15" t="inlineStr">
+      <c r="R5" s="18" t="inlineStr">
         <is>
           <t>（ドライブのリンク）</t>
         </is>
       </c>
-      <c r="T5" s="15" t="inlineStr">
+      <c r="S5" s="18" t="inlineStr">
         <is>
           <t>2026/10/06</t>
         </is>
       </c>
-      <c r="U5" s="15" t="inlineStr">
+      <c r="T5" s="18" t="inlineStr">
         <is>
           <t>16:00-16:40</t>
         </is>
       </c>
-      <c r="V5" s="15" t="inlineStr">
+      <c r="U5" s="18" t="inlineStr">
         <is>
           <t>担当者B</t>
         </is>
       </c>
-      <c r="W5" s="16" t="n">
+      <c r="V5" s="19" t="n">
         <v>18000</v>
       </c>
-      <c r="X5" s="15" t="inlineStr">
+      <c r="W5" s="18" t="inlineStr">
         <is>
           <t>2026/10/06</t>
         </is>
       </c>
-      <c r="Y5" s="15" t="inlineStr">
+      <c r="X5" s="18" t="inlineStr">
         <is>
           <t>16:40-17:30</t>
         </is>
       </c>
-      <c r="Z5" s="15" t="inlineStr">
+      <c r="Y5" s="18" t="inlineStr">
         <is>
           <t>担当者B</t>
         </is>
       </c>
-      <c r="AA5" s="15" t="n">
+      <c r="Z5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="AB5" s="16" t="n">
+      <c r="AA5" s="19" t="n">
         <v>18000</v>
       </c>
-      <c r="AC5" s="15" t="inlineStr">
+      <c r="AB5" s="18" t="inlineStr">
         <is>
           <t>現金</t>
         </is>
       </c>
-      <c r="AD5" s="15" t="inlineStr">
+      <c r="AC5" s="18" t="inlineStr">
         <is>
           <t>済</t>
         </is>
       </c>
-      <c r="AE5" s="15" t="inlineStr">
+      <c r="AD5" s="18" t="inlineStr">
         <is>
           <t>住所・苗字が工番1001と一致したためリピート（奥様が前回依頼）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="X1:AD1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="N1:R1"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="T1:W1"/>
-  </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="13">
     <dataValidation sqref="E3:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>選択肢!$A$2:$A$3</formula1>
     </dataValidation>
@@ -1166,40 +1096,37 @@
       <formula1>選択肢!$B$2:$B$3</formula1>
     </dataValidation>
     <dataValidation sqref="J3:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$C$2:$C$5</formula1>
+      <formula1>選択肢!$C$2:$C$9</formula1>
     </dataValidation>
     <dataValidation sqref="K3:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$D$2:$D$9</formula1>
+      <formula1>選択肢!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="L3:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>選択肢!$G$2:$G$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>選択肢!$H$2:$H$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="N3:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>選択肢!$I$2:$I$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>選択肢!$J$2:$J$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q3:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>選択肢!$K$2:$K$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="U3:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>選択肢!$E$2:$E$4</formula1>
     </dataValidation>
-    <dataValidation sqref="M3:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$H$2:$H$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="N3:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$I$2:$I$10</formula1>
-    </dataValidation>
-    <dataValidation sqref="O3:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$J$2:$J$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="P3:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$K$2:$K$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="R3:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$L$2:$L$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="V3:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y3:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>選択肢!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation sqref="Z3:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$G$2:$G$4</formula1>
+    <dataValidation sqref="AB3:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>選択肢!$L$2:$L$5</formula1>
     </dataValidation>
     <dataValidation sqref="AC3:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$M$2:$M$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="AD3:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>選択肢!$N$2:$N$3</formula1>
+      <formula1>選択肢!$M$2:$M$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1212,7 +1139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1224,1030 +1151,998 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>列</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>グループ</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>列名</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>入力する人</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>形式・選択肢</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="20" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>お客様情報</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>お名前</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>姓名。リピートは住所＋苗字で照合する</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>お客様情報</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>電話番号</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>着信番号を確認して登録</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>お客様情報</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>携帯はSMSで確認し、修正された住所に自動で更新。固定は復唱で確認</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>お客様情報</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>聞き取りの揺れを防ぐため</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>お客様情報</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>電話の種類</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>携帯／固定。住所の確認方法がここで変わる</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>お客様情報</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>新規／リピート</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>自動</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>住所＋苗字が過去の行と一致すれば「リピート」</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>案件の基本</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>工番</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>自動</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>連番（1001〜）</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>案件番号。1つの問い合わせに1つ。お客様情報のすぐ右に置く</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>案件の基本</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>前回の工番</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>自動</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>工番</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>リピートの場合に、そのお客様の直近の工番を入れる。過去の作業をたどる手がかり</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>案件の基本</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>受付日時</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>日時</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>電話を受けた日時</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>案件の基本</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>受付経路</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>AI→担当</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>受付時はAIが「受付（見積前）」か「折り返し待ち」を入れ、以降は担当者が更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>案件の基本</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>対応担当者</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>AI→担当</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>カレンダーで押さえた担当者をAIが入れる。折り返し案件は空欄で、割り振った人が入れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>案件の基本</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>折り返し理由</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>受電AI／担当者直接／Web見積もり／業者紹介</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>案件の基本</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>複数箇所／緊急訪問希望／住所確認できず／対象外の内容／その他。折り返し不要なら空欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>問い合わせ内容</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>カテゴリ</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>トイレ／キッチン／給湯器／換気扇／風呂／その他水回り／水栓・蛇口／電気関係／その他（清水様の工事可能品目の区分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>問い合わせ内容</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>交換・修理／水漏れ／緊急対応。換気扇・電気関係は交換・修理のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>問い合わせ内容</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>複数箇所</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>はい／いいえ</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>「はい」なら日程は担当者から折り返し</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>問い合わせ内容</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>ご用件メモ</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>文字</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>お客様の言葉のまま要約。品目や、駐車・エレベーターなど聞けたことがあればここに残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>問い合わせ内容</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>緊急訪問の希望</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>あり／なし／対象外</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>水回り・給湯器のみ質問。「あり」は担当者へ即通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>写真</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>写真フォルダ</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>自動</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>リンク</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>案件ごとのドライブフォルダ。中に「01_見積もり」「02_工事」を作る。手書き見積書の写真やWeb見積もりのPDFもここに入れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>見積もり</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>見積訪問日</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>AIが押さえた日。折り返し案件は担当者が入れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>見積もり</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>見積訪問時間</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>AI→担当</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>時刻</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>予定はAI（1時間枠）、実際の時刻は担当者が上書き</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>見積もり</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>見積担当</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>AI→担当</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>受付時はAIが「受付（見積前）」か「折り返し待ち」を入れ、以降は担当者が更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>案件の基本</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>対応担当者</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>AI→担当</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>見積もりに行く人</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>見積もり</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>見積金額</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>税込</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>工事・集金</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>工事日</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>工事に行く日</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>工事・集金</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>工事時間</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>時刻</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>入りと出の時刻</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>工事・集金</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>工事担当</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>カレンダーで押さえた担当者をAIが入れる。折り返し案件は空欄で、割り振った人が入れる</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>案件の基本</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>折り返し理由</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>見積担当と別の人のことがある</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>工事・集金</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>訪問回数</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>再見積もり・再工事で増えたら加算（多くて5〜6回）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>工事・集金</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>集金金額</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>工事・集金</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>集金方法</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>選択</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>複数箇所／緊急訪問希望／住所確認できず／対象外の内容／その他。折り返し不要なら空欄</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>問い合わせ内容</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>トイレ／キッチン／給湯器／換気扇／風呂／その他水回り／水栓・蛇口／電気関係／その他（清水様の工事可能品目の区分）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>問い合わせ内容</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>交換・修理／水漏れ／緊急対応。換気扇・電気関係は交換・修理のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>問い合わせ内容</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>複数箇所</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>はい／いいえ</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>「はい」なら日程は担当者から折り返し</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>問い合わせ内容</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>ご用件メモ</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>現金／振込／カード／後日請求</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>工事・集金</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>集金状況</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>未／済</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>お客様の言葉のまま要約。品目や、駐車・エレベーターなど聞けたことがあればここに残す</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>問い合わせ内容</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>緊急訪問の希望</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>あり／なし／対象外</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>水回り・給湯器のみ質問。「あり」は担当者へ即通知</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>写真</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>写真フォルダ</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>自動</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>リンク</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>案件ごとのドライブフォルダ。中に「01_見積もり」「02_工事」を作る。手書き見積書の写真やWeb見積もりのPDFもここに入れる</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>見積もり</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>見積訪問日</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>AIが押さえた日。折り返し案件は担当者が入れる</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>見積もり</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>見積訪問時間</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>AI→担当</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>時刻</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>予定はAI（1時間枠）、実際の時刻は担当者が上書き</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>見積もり</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>見積担当</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>AI→担当</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>見積もりに行く人</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>見積もり</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>見積金額</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>金額</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>税込</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>工事・集金</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>工事日</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>工事に行く日</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>工事・集金</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>工事時間</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>時刻</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>入りと出の時刻</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>工事・集金</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>工事担当</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>見積担当と別の人のことがある</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>工事・集金</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>訪問回数</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>再見積もり・再工事で増えたら加算（多くて5〜6回）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>工事・集金</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>集金金額</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>金額</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>工事・集金</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>集金方法</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>現金／振込／カード／後日請求</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>工事・集金</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>集金状況</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>未／済</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>担当</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>文字</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>社内メモ</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>ステータスの流れ</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>ステータスの流れ</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>受付（見積前） → 折り返し待ち → 見積日確定 → 見積完了 → 工事日確定 → 工事完了　（途中で「再訪問予定」「キャンセル」になることがある）</t>
         </is>
@@ -2264,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2273,83 +2168,77 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>電話の種類</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>新規／リピート</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
-        <is>
-          <t>受付経路</t>
-        </is>
-      </c>
-      <c r="D1" s="19" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="E1" s="19" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>対応担当者</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
+      <c r="E1" s="22" t="inlineStr">
         <is>
           <t>見積担当</t>
         </is>
       </c>
-      <c r="G1" s="19" t="inlineStr">
+      <c r="F1" s="22" t="inlineStr">
         <is>
           <t>工事担当</t>
         </is>
       </c>
-      <c r="H1" s="19" t="inlineStr">
+      <c r="G1" s="22" t="inlineStr">
         <is>
           <t>折り返し理由</t>
         </is>
       </c>
-      <c r="I1" s="19" t="inlineStr">
+      <c r="H1" s="22" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="J1" s="19" t="inlineStr">
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="K1" s="19" t="inlineStr">
+      <c r="J1" s="22" t="inlineStr">
         <is>
           <t>複数箇所</t>
         </is>
       </c>
-      <c r="L1" s="19" t="inlineStr">
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>緊急訪問の希望</t>
         </is>
       </c>
-      <c r="M1" s="19" t="inlineStr">
+      <c r="L1" s="22" t="inlineStr">
         <is>
           <t>集金方法</t>
         </is>
       </c>
-      <c r="N1" s="19" t="inlineStr">
+      <c r="M1" s="22" t="inlineStr">
         <is>
           <t>集金状況</t>
         </is>
@@ -2368,12 +2257,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>受電AI</t>
+          <t>受付（見積前）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>受付（見積前）</t>
+          <t>清水</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2388,40 +2277,35 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>清水</t>
+          <t>複数箇所</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>複数箇所</t>
+          <t>トイレ</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>トイレ</t>
+          <t>交換・修理</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>交換・修理</t>
+          <t>はい</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>はい</t>
+          <t>あり</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>あり</t>
+          <t>現金</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>現金</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
         <is>
           <t>未</t>
         </is>
@@ -2440,12 +2324,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>担当者直接</t>
+          <t>折り返し待ち</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>折り返し待ち</t>
+          <t>担当者B</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2460,40 +2344,35 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>担当者B</t>
+          <t>緊急訪問希望</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>緊急訪問希望</t>
+          <t>キッチン</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>キッチン</t>
+          <t>水漏れ</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>水漏れ</t>
+          <t>いいえ</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>いいえ</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>振込</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>振込</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
         <is>
           <t>済</t>
         </is>
@@ -2502,12 +2381,12 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>Web見積もり</t>
+          <t>見積日確定</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>見積日確定</t>
+          <t>担当者C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2522,30 +2401,25 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>担当者C</t>
+          <t>住所確認できず</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>住所確認できず</t>
+          <t>給湯器</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>給湯器</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
           <t>緊急対応</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>カード</t>
         </is>
@@ -2554,85 +2428,80 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>業者紹介</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>見積完了</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>対象外の内容</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>対象外の内容</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
           <t>換気扇</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>後日請求</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>工事日確定</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
           <t>風呂</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>工事完了</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>その他水回り</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="D8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>再訪問予定</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>水栓・蛇口</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="D9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>キャンセル</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>電気関係</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="I10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
